--- a/enrollment/fileTemplates/student&sectionTemplates/section(XLSX).xlsx
+++ b/enrollment/fileTemplates/student&sectionTemplates/section(XLSX).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d725c04a17b73256/Documents/Programming/VSCode/CAPSTONE-preEnrollment/preEnrollmentV6.2/enrollment/fileTemplates/student^0sectionTemplates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d725c04a17b73256/Documents/Pre Enrollment File Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{C7E41EB0-3EFC-47A2-B84F-A7BFFB84906F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E995CC3F-82CE-4673-9E2B-20BCFA9467A1}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="13_ncr:1_{C7E41EB0-3EFC-47A2-B84F-A7BFFB84906F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75BF71B1-0012-4BBC-986E-C0E479BFFBC0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{32C72668-5EA3-4148-AB22-E6FC3855149B}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Enrolled</t>
   </si>
@@ -37,79 +37,73 @@
     <t>YEAR</t>
   </si>
   <si>
-    <t>SECTION</t>
-  </si>
-  <si>
     <t>SEMESTER</t>
   </si>
   <si>
     <t>STATUS</t>
   </si>
   <si>
-    <t>Z</t>
-  </si>
-  <si>
     <t>2nd</t>
   </si>
   <si>
-    <t>Jamorie</t>
-  </si>
-  <si>
-    <t>Corry</t>
-  </si>
-  <si>
-    <t>Ferry</t>
-  </si>
-  <si>
-    <t>Evelyn</t>
-  </si>
-  <si>
-    <t>Harold</t>
-  </si>
-  <si>
-    <t>Fundi</t>
-  </si>
-  <si>
-    <t>Dela Gueva</t>
-  </si>
-  <si>
-    <t>Emirates</t>
-  </si>
-  <si>
-    <t>Mercado</t>
-  </si>
-  <si>
-    <t>Dizon</t>
-  </si>
-  <si>
-    <t>Ryzza Mae</t>
-  </si>
-  <si>
-    <t>Constance Angeline</t>
-  </si>
-  <si>
-    <t>Yelena Arabia</t>
-  </si>
-  <si>
-    <t>Zalry Jean</t>
-  </si>
-  <si>
-    <t>Jumaira Queen</t>
-  </si>
-  <si>
-    <t>Residente</t>
-  </si>
-  <si>
-    <t>Severino</t>
-  </si>
-  <si>
-    <t>Al Gaib</t>
-  </si>
-  <si>
-    <t>Sait</t>
-  </si>
-  <si>
-    <t>Parat</t>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>Jennifer</t>
+  </si>
+  <si>
+    <t>Velasquez</t>
+  </si>
+  <si>
+    <t>Cristine</t>
+  </si>
+  <si>
+    <t>Salazar</t>
+  </si>
+  <si>
+    <t>William John</t>
+  </si>
+  <si>
+    <t>Kalinao</t>
+  </si>
+  <si>
+    <t>Atienza</t>
+  </si>
+  <si>
+    <t>Brian Keith</t>
+  </si>
+  <si>
+    <t>Saligo</t>
+  </si>
+  <si>
+    <t>John Mark</t>
+  </si>
+  <si>
+    <t>Naligao</t>
+  </si>
+  <si>
+    <t>Mark Bryan</t>
+  </si>
+  <si>
+    <t>Dela Cruz</t>
+  </si>
+  <si>
+    <t>Xeniel</t>
+  </si>
+  <si>
+    <t>Dimaguiba</t>
+  </si>
+  <si>
+    <t>Saia</t>
+  </si>
+  <si>
+    <t>De Leon</t>
+  </si>
+  <si>
+    <t>Ynna Anne</t>
+  </si>
+  <si>
+    <t>Nuqabah</t>
   </si>
 </sst>
 </file>
@@ -985,15 +979,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F329A3CF-F485-47C1-B091-9F3169CDB046}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
     <col min="2" max="3" width="12.77734375" customWidth="1"/>
-    <col min="4" max="7" width="9.77734375" customWidth="1"/>
+    <col min="4" max="6" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1012,339 +1006,306 @@
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>202610082</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>202110017</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>202110018</v>
+        <v>202610083</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>202610084</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>202610085</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>202610086</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>202110019</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>202610087</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>202610088</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>202610089</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>202110020</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>202610090</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>202110021</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>202610091</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>202110022</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>202110023</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>202110024</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>202110025</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>202110026</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
-      <c r="F31" s="2"/>
+      <c r="E31" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
